--- a/docs/downloads/purview-administrator-checklist.xlsx
+++ b/docs/downloads/purview-administrator-checklist.xlsx
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Purview Compliance Admin  |  FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>Role: Purview Compliance Admin  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CPurview Administrator Checklist</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/docs/downloads/purview-administrator-checklist.xlsx
+++ b/docs/downloads/purview-administrator-checklist.xlsx
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Purview Compliance Admin  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>Role: Purview Compliance Admin  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -711,10 +711,11 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="7" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/purview-administrator-checklist.xlsx
+++ b/docs/downloads/purview-administrator-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purview Compliance Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Purview Compliance Admin'!$A$4:$E$4</definedName>
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Purview Compliance Admin  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>Role: Purview Compliance Admin  |  FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Microsoft Purview: DSPM for AI</t>
+          <t>Microsoft Purview DSPM for AI</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/purview-administrator-checklist.xlsx
+++ b/docs/downloads/purview-administrator-checklist.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Microsoft Purview DSPM for AI</t>
+          <t>Microsoft Purview: DSPM for AI</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
